--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/COLORADO_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/COLORADO_2021.xlsx
@@ -1687,7 +1687,7 @@
         <v>10</v>
       </c>
       <c r="D74">
-        <v>0.0009026900162484203</v>
+        <v>0.0009026900162484204</v>
       </c>
     </row>
     <row r="75">
@@ -1705,7 +1705,7 @@
         <v>10</v>
       </c>
       <c r="D75">
-        <v>0.0009026900162484203</v>
+        <v>0.0009026900162484204</v>
       </c>
     </row>
     <row r="76">
@@ -1921,7 +1921,7 @@
         <v>10</v>
       </c>
       <c r="D87">
-        <v>0.0009026900162484203</v>
+        <v>0.0009026900162484204</v>
       </c>
     </row>
     <row r="88">
@@ -2173,7 +2173,7 @@
         <v>10</v>
       </c>
       <c r="D101">
-        <v>0.0009026900162484203</v>
+        <v>0.0009026900162484204</v>
       </c>
     </row>
     <row r="102">
@@ -3037,7 +3037,7 @@
         <v>109</v>
       </c>
       <c r="D149">
-        <v>0.009839321177107781</v>
+        <v>0.00983932117710778</v>
       </c>
     </row>
     <row r="150">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C181">
@@ -3667,7 +3667,7 @@
         <v>10</v>
       </c>
       <c r="D184">
-        <v>0.0009026900162484203</v>
+        <v>0.0009026900162484204</v>
       </c>
     </row>
     <row r="185">
@@ -4027,7 +4027,7 @@
         <v>10</v>
       </c>
       <c r="D204">
-        <v>0.0009026900162484203</v>
+        <v>0.0009026900162484204</v>
       </c>
     </row>
     <row r="205">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C283">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C291">
@@ -6115,7 +6115,7 @@
         <v>10</v>
       </c>
       <c r="D320">
-        <v>0.0009026900162484203</v>
+        <v>0.0009026900162484204</v>
       </c>
     </row>
     <row r="321">
@@ -6979,7 +6979,7 @@
         <v>10</v>
       </c>
       <c r="D368">
-        <v>0.0009026900162484203</v>
+        <v>0.0009026900162484204</v>
       </c>
     </row>
     <row r="369">
@@ -6997,7 +6997,7 @@
         <v>10</v>
       </c>
       <c r="D369">
-        <v>0.0009026900162484203</v>
+        <v>0.0009026900162484204</v>
       </c>
     </row>
     <row r="370">
@@ -10201,7 +10201,7 @@
         <v>10</v>
       </c>
       <c r="D547">
-        <v>0.0009026900162484203</v>
+        <v>0.0009026900162484204</v>
       </c>
     </row>
     <row r="548">
@@ -11443,7 +11443,7 @@
         <v>10</v>
       </c>
       <c r="D616">
-        <v>0.0009026900162484203</v>
+        <v>0.0009026900162484204</v>
       </c>
     </row>
     <row r="617">
@@ -13254,7 +13254,7 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C717">
@@ -13488,7 +13488,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C730">
@@ -13560,7 +13560,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C734">
@@ -16213,7 +16213,7 @@
         <v>10</v>
       </c>
       <c r="D881">
-        <v>0.0009026900162484203</v>
+        <v>0.0009026900162484204</v>
       </c>
     </row>
     <row r="882">
@@ -19795,7 +19795,7 @@
         <v>10</v>
       </c>
       <c r="D1080">
-        <v>0.0009026900162484203</v>
+        <v>0.0009026900162484204</v>
       </c>
     </row>
     <row r="1081">
